--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee11846ce882123f/Desktop/hem-catalogue-app_final-1/hem-catalogue-app-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A8AAAD60-69E8-4262-8E76-0BDF9841794C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40000671-B39B-4837-B19C-59590E020029}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478C4E3F-C5EB-4338-8716-16C1C669B462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="191">
   <si>
     <t>Description</t>
   </si>
@@ -86,9 +86,6 @@
     <t>12 doz</t>
   </si>
   <si>
-    <t>PREMIUM MASALA INCENSE HEXA</t>
-  </si>
-  <si>
     <t>15 Sticks in a packet, 6 packet in a box,  2 boxes make 1 Dozen</t>
   </si>
   <si>
@@ -104,9 +101,6 @@
     <t>0.060</t>
   </si>
   <si>
-    <t>NEW AGE MASALA            15 GMS</t>
-  </si>
-  <si>
     <t>15 Grams in a packet, 12 Packs (1 dozen) in a box, 288 Packs (24 dozen) in a master carton</t>
   </si>
   <si>
@@ -120,12 +114,6 @@
   </si>
   <si>
     <t xml:space="preserve">NATURE MASALA GIFT PACK </t>
-  </si>
-  <si>
-    <t>SMUDGING INDULGENCE MASALA GIFT PACK(Palo Santo premium Incense blends &amp; Chakras Energy Balancing Bracele)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 packs of blends with 1 Bracelet. Each pack consist 15 sticks.                                                Assortment consist of Palo Santo Sandal, Palo Santo Aruda, Palo Santo Cinnamon, Palo Santo Myrrh, Palo Santo Rose. </t>
   </si>
   <si>
     <t>5 Hexa Packet in an outer packet</t>
@@ -242,20 +230,11 @@
     <t>20 Jumbo Cones in one Pack, 12 Packet in one box, 6 Box in one master Carton</t>
   </si>
   <si>
-    <t>BACKFLOW CONE BURNER GIFT SET     Design Name:
-1)Plate Fountain
-2)Wall Fountain
-3)OM</t>
-  </si>
-  <si>
     <t>1 pack contain 1pcs of holder &amp; 10 pcs of cones.
 12 pcs in 1 Master Carton</t>
   </si>
   <si>
     <t>1 doz</t>
-  </si>
-  <si>
-    <t>7 CHAKRA STONE</t>
   </si>
   <si>
     <t>7 Diffrenet types of Stones in one pack.
@@ -478,9 +457,6 @@
     <t>Masala 15 Gm 40 Doz</t>
   </si>
   <si>
-    <t xml:space="preserve"> HEXA GIFT PACK</t>
-  </si>
-  <si>
     <t>Square 48 Box (OP)</t>
   </si>
   <si>
@@ -620,6 +596,33 @@
   </si>
   <si>
     <t>30 Dz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 packs of blends with 1 Bracelet. Each pack consist 15 sticks.   Assortment consist of Palo Santo Sandal, Palo Santo Aruda, Palo Santo Cinnamon, Palo Santo Myrrh, Palo Santo Rose. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GIFT PACK</t>
+  </si>
+  <si>
+    <t>Hexa Packet in an outer packet</t>
+  </si>
+  <si>
+    <t>24 Pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BACKFLOW CONE BURNER GIFT SET     </t>
+  </si>
+  <si>
+    <t>SMUDGING INDULGENCE MASALA GIFT PACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 CHAKRA </t>
+  </si>
+  <si>
+    <t>NEW AGE MASALA 15 GMS</t>
+  </si>
+  <si>
+    <t>PREMIUM MASALA INCENSE (Hexa 15Stik)</t>
   </si>
 </sst>
 </file>
@@ -687,7 +690,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -906,15 +909,6 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -936,7 +930,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -993,9 +987,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1122,38 +1113,53 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2679,56 +2685,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42" style="13" customWidth="1"/>
-    <col min="4" max="4" width="26.26953125" style="13" customWidth="1"/>
-    <col min="5" max="5" width="8.36328125" style="13" customWidth="1"/>
-    <col min="6" max="6" width="7.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.453125" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.08984375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="33" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="15" t="s">
-        <v>8</v>
+      <c r="A2" s="70" t="s">
+        <v>183</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
@@ -2736,260 +2742,260 @@
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="35">
+      <c r="D2" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="34">
         <v>16.5</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="34">
         <v>15.5</v>
       </c>
-      <c r="G2" s="35">
+      <c r="G2" s="34">
         <v>46.5</v>
       </c>
-      <c r="H2" s="35">
+      <c r="H2" s="34">
         <v>32.5</v>
       </c>
-      <c r="I2" s="35">
+      <c r="I2" s="34">
         <v>53.5</v>
       </c>
-      <c r="J2" s="36">
+      <c r="J2" s="35">
         <v>8.0851875000000004E-2</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="70" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="34">
+        <v>15.8</v>
+      </c>
+      <c r="F3" s="34">
+        <v>14.7</v>
+      </c>
+      <c r="G3" s="34">
+        <v>40</v>
+      </c>
+      <c r="H3" s="34">
+        <v>39</v>
+      </c>
+      <c r="I3" s="34">
+        <v>54</v>
+      </c>
+      <c r="J3" s="35">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="70" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="34">
+        <v>13</v>
+      </c>
+      <c r="F4" s="34">
+        <v>12</v>
+      </c>
+      <c r="G4" s="34">
+        <v>38</v>
+      </c>
+      <c r="H4" s="34">
+        <v>32</v>
+      </c>
+      <c r="I4" s="34">
+        <v>54</v>
+      </c>
+      <c r="J4" s="35">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="70" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="34">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="35">
-        <v>15.8</v>
-      </c>
-      <c r="F3" s="35">
-        <v>14.7</v>
-      </c>
-      <c r="G3" s="35">
-        <v>40</v>
-      </c>
-      <c r="H3" s="35">
-        <v>39</v>
-      </c>
-      <c r="I3" s="35">
-        <v>54</v>
-      </c>
-      <c r="J3" s="36">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="35">
-        <v>13</v>
-      </c>
-      <c r="F4" s="35">
-        <v>12</v>
-      </c>
-      <c r="G4" s="35">
-        <v>38</v>
-      </c>
-      <c r="H4" s="35">
-        <v>32</v>
-      </c>
-      <c r="I4" s="35">
-        <v>54</v>
-      </c>
-      <c r="J4" s="36">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E5" s="35">
-        <v>8</v>
-      </c>
-      <c r="F5" s="35">
+      <c r="F5" s="34">
         <v>7.4</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="34">
         <v>57.5</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="34">
         <v>25</v>
       </c>
-      <c r="I5" s="35">
+      <c r="I5" s="34">
         <v>27.5</v>
       </c>
-      <c r="J5" s="36">
+      <c r="J5" s="35">
         <v>0.04</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="35">
+        <v>125</v>
+      </c>
+      <c r="E6" s="34">
         <v>4</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="34">
         <v>3.5</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="34">
         <v>38</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="34">
         <v>27</v>
       </c>
-      <c r="I6" s="35">
+      <c r="I6" s="34">
         <v>20</v>
       </c>
-      <c r="J6" s="36">
+      <c r="J6" s="35">
         <v>0.02</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="15" t="s">
-        <v>11</v>
+      <c r="A7" s="16" t="s">
+        <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" s="35">
+        <v>67</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="34">
         <v>16.5</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="34">
         <v>15.3</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="34">
         <v>60</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="34">
         <v>36</v>
       </c>
-      <c r="I7" s="35">
+      <c r="I7" s="34">
         <v>45</v>
       </c>
-      <c r="J7" s="36">
+      <c r="J7" s="35">
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="15" t="s">
-        <v>11</v>
+      <c r="A8" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E8" s="35">
+        <v>126</v>
+      </c>
+      <c r="E8" s="34">
         <v>15</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="34">
         <v>14.1</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="34">
         <f>_xlfn.XLOOKUP(D8,'[1]Master_infoCase_Size (2)'!$A$96:$A$256,'[1]Master_infoCase_Size (2)'!$G$96:$G$256,"")</f>
         <v>45.1</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="34">
         <v>36.5</v>
       </c>
-      <c r="I8" s="35">
+      <c r="I8" s="34">
         <v>44.5</v>
       </c>
-      <c r="J8" s="36">
+      <c r="J8" s="35">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="15" t="s">
-        <v>11</v>
+      <c r="A9" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" s="35">
+        <v>127</v>
+      </c>
+      <c r="E9" s="34">
         <v>9</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="34">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="34">
         <f>_xlfn.XLOOKUP(D9,'[1]Master_infoCase_Size (2)'!$A$96:$A$256,'[1]Master_infoCase_Size (2)'!$G$96:$G$256,"")</f>
         <v>36</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="34">
         <v>30</v>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="34">
         <v>44</v>
       </c>
-      <c r="J9" s="36">
+      <c r="J9" s="35">
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
@@ -2997,583 +3003,583 @@
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="34">
         <v>16.5</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="34">
         <v>15.5</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="34">
         <v>46.5</v>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="34">
         <v>32.5</v>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="34">
         <v>53.5</v>
       </c>
-      <c r="J10" s="36">
+      <c r="J10" s="35">
         <v>8.0851875000000004E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="36">
+        <v>10.3</v>
+      </c>
+      <c r="F11" s="36">
+        <v>9.6</v>
+      </c>
+      <c r="G11" s="21">
+        <v>49</v>
+      </c>
+      <c r="H11" s="21">
+        <v>27</v>
+      </c>
+      <c r="I11" s="21">
+        <v>45</v>
+      </c>
+      <c r="J11" s="21" t="s">
         <v>18</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E11" s="37">
-        <v>10.3</v>
-      </c>
-      <c r="F11" s="37">
-        <v>9.6</v>
-      </c>
-      <c r="G11" s="22">
-        <v>49</v>
-      </c>
-      <c r="H11" s="22">
-        <v>27</v>
-      </c>
-      <c r="I11" s="22">
-        <v>45</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="17" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="36">
+        <v>21</v>
+      </c>
+      <c r="F12" s="36">
+        <v>20</v>
+      </c>
+      <c r="G12" s="36">
+        <v>66</v>
+      </c>
+      <c r="H12" s="36">
+        <v>42</v>
+      </c>
+      <c r="I12" s="21">
+        <v>47</v>
+      </c>
+      <c r="J12" s="21">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="71" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" s="36">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="F13" s="36">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G13" s="36">
+        <v>27</v>
+      </c>
+      <c r="H13" s="36">
+        <v>25.4</v>
+      </c>
+      <c r="I13" s="21">
+        <v>24</v>
+      </c>
+      <c r="J13" s="21">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E12" s="37">
+      <c r="D14" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E14" s="36">
+        <v>10.3</v>
+      </c>
+      <c r="F14" s="36">
+        <v>9.6</v>
+      </c>
+      <c r="G14" s="36">
+        <v>49</v>
+      </c>
+      <c r="H14" s="36">
+        <v>27</v>
+      </c>
+      <c r="I14" s="21">
+        <v>45</v>
+      </c>
+      <c r="J14" s="21">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="36">
+        <v>12.75</v>
+      </c>
+      <c r="F15" s="36">
+        <v>10.75</v>
+      </c>
+      <c r="G15" s="36">
+        <v>41.5</v>
+      </c>
+      <c r="H15" s="36">
+        <v>40</v>
+      </c>
+      <c r="I15" s="21">
+        <v>47.5</v>
+      </c>
+      <c r="J15" s="21">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="36">
+        <v>22.87</v>
+      </c>
+      <c r="F16" s="36">
+        <v>21.9</v>
+      </c>
+      <c r="G16" s="36">
+        <v>50.5</v>
+      </c>
+      <c r="H16" s="36">
+        <v>34</v>
+      </c>
+      <c r="I16" s="21">
+        <v>51</v>
+      </c>
+      <c r="J16" s="21">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="36">
+        <v>10.3</v>
+      </c>
+      <c r="F17" s="36">
+        <v>9.6</v>
+      </c>
+      <c r="G17" s="21">
+        <v>49</v>
+      </c>
+      <c r="H17" s="21">
+        <v>27</v>
+      </c>
+      <c r="I17" s="21">
+        <v>45</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="37">
-        <v>20</v>
-      </c>
-      <c r="G12" s="37">
-        <v>66</v>
-      </c>
-      <c r="H12" s="37">
-        <v>42</v>
-      </c>
-      <c r="I12" s="22">
-        <v>47</v>
-      </c>
-      <c r="J12" s="22">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" s="37">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="F13" s="37">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G13" s="37">
-        <v>27</v>
-      </c>
-      <c r="H13" s="37">
-        <v>25.4</v>
-      </c>
-      <c r="I13" s="22">
-        <v>24</v>
-      </c>
-      <c r="J13" s="22">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" s="37">
-        <v>10.3</v>
-      </c>
-      <c r="F14" s="37">
-        <v>9.6</v>
-      </c>
-      <c r="G14" s="37">
-        <v>49</v>
-      </c>
-      <c r="H14" s="37">
-        <v>27</v>
-      </c>
-      <c r="I14" s="22">
-        <v>45</v>
-      </c>
-      <c r="J14" s="22">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" s="37">
-        <v>12.75</v>
-      </c>
-      <c r="F15" s="37">
-        <v>10.75</v>
-      </c>
-      <c r="G15" s="37">
-        <v>41.5</v>
-      </c>
-      <c r="H15" s="37">
-        <v>40</v>
-      </c>
-      <c r="I15" s="22">
-        <v>47.5</v>
-      </c>
-      <c r="J15" s="22">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" s="37">
-        <v>22.87</v>
-      </c>
-      <c r="F16" s="37">
-        <v>21.9</v>
-      </c>
-      <c r="G16" s="37">
-        <v>50.5</v>
-      </c>
-      <c r="H16" s="37">
-        <v>34</v>
-      </c>
-      <c r="I16" s="22">
-        <v>51</v>
-      </c>
-      <c r="J16" s="22">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="37">
-        <v>10.3</v>
-      </c>
-      <c r="F17" s="37">
-        <v>9.6</v>
-      </c>
-      <c r="G17" s="22">
-        <v>49</v>
-      </c>
-      <c r="H17" s="22">
-        <v>27</v>
-      </c>
-      <c r="I17" s="22">
-        <v>45</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="16" t="s">
+      <c r="C18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="35">
+        <v>22</v>
+      </c>
+      <c r="E18" s="34">
         <v>13.8</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="34">
         <v>12.8</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="34">
         <v>58.5</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="34">
         <v>31</v>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="34">
         <v>51.2</v>
       </c>
-      <c r="J18" s="36">
+      <c r="J18" s="35">
         <f>+G18*H18*I18/1000000</f>
         <v>9.2851200000000009E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="16" t="s">
-        <v>25</v>
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="70" t="s">
+        <v>50</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="35">
+        <v>22</v>
+      </c>
+      <c r="E19" s="34">
         <v>13.8</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="34">
         <v>12.8</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="34">
         <v>58.5</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="34">
         <v>31</v>
       </c>
-      <c r="I19" s="35">
+      <c r="I19" s="34">
         <v>51.2</v>
       </c>
-      <c r="J19" s="36">
+      <c r="J19" s="35">
         <f>+G19*H19*I19/1000000</f>
         <v>9.2851200000000009E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="16" t="s">
+    <row r="20" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="69" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="34">
+        <v>20.5</v>
+      </c>
+      <c r="F20" s="34">
+        <v>19</v>
+      </c>
+      <c r="G20" s="34">
+        <v>46.5</v>
+      </c>
+      <c r="H20" s="34">
+        <v>40.5</v>
+      </c>
+      <c r="I20" s="34">
+        <v>48</v>
+      </c>
+      <c r="J20" s="35">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="36">
+        <v>16.7</v>
+      </c>
+      <c r="F21" s="36">
+        <v>15.2</v>
+      </c>
+      <c r="G21" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="H21" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="35">
-        <v>20.5</v>
-      </c>
-      <c r="F20" s="35">
-        <v>19</v>
-      </c>
-      <c r="G20" s="35">
-        <v>46.5</v>
-      </c>
-      <c r="H20" s="35">
-        <v>40.5</v>
-      </c>
-      <c r="I20" s="35">
-        <v>48</v>
-      </c>
-      <c r="J20" s="36">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="60" t="s">
-        <v>141</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="I21" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D21" s="23" t="s">
+      <c r="J21" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="37">
-        <v>16.7</v>
-      </c>
-      <c r="F21" s="37">
-        <v>15.2</v>
-      </c>
-      <c r="G21" s="22" t="s">
+    </row>
+    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="C22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="22" t="s">
+      <c r="E22" s="37">
+        <v>16.3</v>
+      </c>
+      <c r="F22" s="37">
+        <v>15.1</v>
+      </c>
+      <c r="G22" s="37">
+        <v>41</v>
+      </c>
+      <c r="H22" s="37">
+        <v>36.5</v>
+      </c>
+      <c r="I22" s="37">
+        <v>53</v>
+      </c>
+      <c r="J22" s="38">
+        <v>7.9073820000000003E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="60" t="s">
-        <v>141</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="C23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="39">
+        <v>23.4</v>
+      </c>
+      <c r="F23" s="39">
+        <v>22.4</v>
+      </c>
+      <c r="G23" s="39">
+        <v>41.5</v>
+      </c>
+      <c r="H23" s="39">
+        <v>33.5</v>
+      </c>
+      <c r="I23" s="39">
+        <v>48.5</v>
+      </c>
+      <c r="J23" s="40">
+        <v>6.7427125000000004E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="38">
+      <c r="C24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="34">
         <v>16.3</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F24" s="34">
         <v>15.1</v>
       </c>
-      <c r="G22" s="38">
-        <v>41</v>
-      </c>
-      <c r="H22" s="38">
-        <v>36.5</v>
-      </c>
-      <c r="I22" s="38">
+      <c r="G24" s="34">
+        <v>42</v>
+      </c>
+      <c r="H24" s="34">
+        <v>36</v>
+      </c>
+      <c r="I24" s="34">
         <v>53</v>
       </c>
-      <c r="J22" s="39">
-        <v>7.9073820000000003E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="60" t="s">
-        <v>141</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="40">
-        <v>23.4</v>
-      </c>
-      <c r="F23" s="40">
-        <v>22.4</v>
-      </c>
-      <c r="G23" s="40">
-        <v>41.5</v>
-      </c>
-      <c r="H23" s="40">
-        <v>33.5</v>
-      </c>
-      <c r="I23" s="40">
-        <v>48.5</v>
-      </c>
-      <c r="J23" s="41">
-        <v>6.7427125000000004E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="35">
-        <v>16.3</v>
-      </c>
-      <c r="F24" s="35">
-        <v>15.1</v>
-      </c>
-      <c r="G24" s="35">
-        <v>42</v>
-      </c>
-      <c r="H24" s="35">
-        <v>36</v>
-      </c>
-      <c r="I24" s="35">
-        <v>53</v>
-      </c>
-      <c r="J24" s="36">
+      <c r="J24" s="35">
         <f t="shared" ref="J24" si="0">+G24*H24*I24/1000000</f>
         <v>8.0135999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="16" t="s">
-        <v>39</v>
+    <row r="25" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="70" t="s">
+        <v>50</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="34">
+        <v>15.3</v>
+      </c>
+      <c r="F25" s="34">
+        <v>14.3</v>
+      </c>
+      <c r="G25" s="34">
+        <v>42.5</v>
+      </c>
+      <c r="H25" s="34">
         <v>40</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="35">
-        <v>15.3</v>
-      </c>
-      <c r="F25" s="35">
-        <v>14.3</v>
-      </c>
-      <c r="G25" s="35">
-        <v>42.5</v>
-      </c>
-      <c r="H25" s="35">
-        <v>40</v>
-      </c>
-      <c r="I25" s="35">
+      <c r="I25" s="34">
         <v>54.5</v>
       </c>
-      <c r="J25" s="36">
+      <c r="J25" s="35">
         <v>9.2766407999999995E-2</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="35">
+        <v>40</v>
+      </c>
+      <c r="E26" s="34">
         <v>11.5</v>
       </c>
-      <c r="F26" s="35">
+      <c r="F26" s="34">
         <v>10.9</v>
       </c>
-      <c r="G26" s="35">
+      <c r="G26" s="34">
         <v>46</v>
       </c>
-      <c r="H26" s="35">
+      <c r="H26" s="34">
         <v>40.5</v>
       </c>
-      <c r="I26" s="35">
+      <c r="I26" s="34">
         <v>47</v>
       </c>
-      <c r="J26" s="36">
+      <c r="J26" s="35">
         <f>G26*H26*I26/1000000</f>
         <v>8.7561E-2</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="60" t="s">
-        <v>45</v>
+      <c r="A27" s="59" t="s">
+        <v>76</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="35">
+        <v>43</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="34">
         <v>23</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="34">
         <v>21.5</v>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="34">
         <v>41.5</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="34">
         <v>41.5</v>
       </c>
-      <c r="I27" s="35">
+      <c r="I27" s="34">
         <v>54.7</v>
       </c>
-      <c r="J27" s="36">
+      <c r="J27" s="35">
         <v>9.4207075000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="60" t="s">
-        <v>45</v>
+      <c r="A28" s="59" t="s">
+        <v>72</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E28" s="6">
         <v>23</v>
@@ -3590,20 +3596,20 @@
       <c r="I28" s="6">
         <v>54</v>
       </c>
-      <c r="J28" s="36">
+      <c r="J28" s="35">
         <v>0.11</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="60" t="s">
-        <v>45</v>
+      <c r="A29" s="76" t="s">
+        <v>103</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E29" s="6">
         <v>29.2</v>
@@ -3620,20 +3626,20 @@
       <c r="I29" s="6">
         <v>54</v>
       </c>
-      <c r="J29" s="36">
+      <c r="J29" s="35">
         <v>0.13</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="60" t="s">
-        <v>45</v>
+      <c r="A30" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E30" s="6">
         <v>17</v>
@@ -3650,20 +3656,20 @@
       <c r="I30" s="6">
         <v>55</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="35">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="60" t="s">
-        <v>45</v>
+      <c r="A31" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E31" s="6">
         <v>23</v>
@@ -3680,20 +3686,20 @@
       <c r="I31" s="6">
         <v>54.7</v>
       </c>
-      <c r="J31" s="36">
+      <c r="J31" s="35">
         <v>0.1</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="60" t="s">
-        <v>45</v>
+      <c r="A32" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E32" s="6">
         <v>12</v>
@@ -3710,20 +3716,20 @@
       <c r="I32" s="6">
         <v>28</v>
       </c>
-      <c r="J32" s="36">
+      <c r="J32" s="35">
         <v>0.05</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="60" t="s">
-        <v>45</v>
+      <c r="A33" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E33" s="6">
         <v>11</v>
@@ -3740,150 +3746,150 @@
       <c r="I33" s="6">
         <v>34</v>
       </c>
-      <c r="J33" s="36">
+      <c r="J33" s="35">
         <v>0.05</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="18" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" s="42">
+        <v>46</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="41">
         <v>14.2</v>
       </c>
-      <c r="F34" s="42">
+      <c r="F34" s="41">
         <v>15.2</v>
       </c>
-      <c r="G34" s="43">
+      <c r="G34" s="42">
         <v>52.5</v>
       </c>
-      <c r="H34" s="43">
+      <c r="H34" s="42">
         <v>27</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="42">
         <v>45</v>
       </c>
-      <c r="J34" s="36">
+      <c r="J34" s="35">
         <f>G34*H34*I34/1000000</f>
         <v>6.3787499999999997E-2</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="16" t="s">
-        <v>51</v>
+      <c r="A35" s="15" t="s">
+        <v>110</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" s="35">
+        <v>49</v>
+      </c>
+      <c r="E35" s="34">
         <v>17.925000000000001</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="34">
         <v>16.399999999999999</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="34">
         <v>56</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="34">
         <v>36</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="34">
         <v>53.5</v>
       </c>
-      <c r="J35" s="36">
+      <c r="J35" s="35">
         <f>G35*H35*I35/1000000</f>
         <v>0.10785599999999999</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="60" t="s">
+      <c r="A36" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="36">
+        <v>10.4</v>
+      </c>
+      <c r="F36" s="36">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G36" s="43">
+        <v>34.5</v>
+      </c>
+      <c r="H36" s="43">
+        <v>26.5</v>
+      </c>
+      <c r="I36" s="43">
+        <v>48</v>
+      </c>
+      <c r="J36" s="44">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D37" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="E36" s="37">
-        <v>10.4</v>
-      </c>
-      <c r="F36" s="37">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="G36" s="44">
-        <v>34.5</v>
-      </c>
-      <c r="H36" s="44">
-        <v>26.5</v>
-      </c>
-      <c r="I36" s="44">
-        <v>48</v>
-      </c>
-      <c r="J36" s="45">
-        <v>4.3999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="60" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="E37" s="37">
+      <c r="E37" s="36">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F37" s="37">
+      <c r="F37" s="36">
         <v>7.5</v>
       </c>
-      <c r="G37" s="44">
+      <c r="G37" s="43">
         <v>38</v>
       </c>
-      <c r="H37" s="44">
+      <c r="H37" s="43">
         <v>33.5</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="43">
         <v>28.5</v>
       </c>
-      <c r="J37" s="45">
+      <c r="J37" s="44">
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="60" t="s">
-        <v>54</v>
+      <c r="A38" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E38" s="6">
         <v>10.199999999999999</v>
@@ -3905,15 +3911,15 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="60" t="s">
-        <v>54</v>
+      <c r="A39" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E39" s="6">
         <v>11.5</v>
@@ -3935,15 +3941,15 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="60" t="s">
-        <v>54</v>
+      <c r="A40" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E40" s="6">
         <v>10.199999999999999</v>
@@ -3965,15 +3971,15 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="60" t="s">
-        <v>54</v>
+      <c r="A41" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E41" s="6">
         <v>8.3000000000000007</v>
@@ -3995,15 +4001,15 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="60" t="s">
-        <v>54</v>
+      <c r="A42" s="76" t="s">
+        <v>55</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E42" s="6">
         <v>10.199999999999999</v>
@@ -4026,726 +4032,735 @@
     </row>
     <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B43" s="56" t="s">
-        <v>55</v>
+        <v>23</v>
+      </c>
+      <c r="B43" s="55" t="s">
+        <v>51</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" s="56" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="42">
+        <v>17</v>
+      </c>
+      <c r="D43" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="41">
         <v>13.5</v>
       </c>
-      <c r="F43" s="42">
+      <c r="F43" s="41">
         <v>12.4</v>
       </c>
-      <c r="G43" s="42">
+      <c r="G43" s="41">
         <v>47.5</v>
       </c>
-      <c r="H43" s="42">
+      <c r="H43" s="41">
         <v>44.3</v>
       </c>
-      <c r="I43" s="42">
+      <c r="I43" s="41">
         <v>32.5</v>
       </c>
-      <c r="J43" s="57">
+      <c r="J43" s="56">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="62" t="s">
-        <v>60</v>
+      <c r="A44" s="76" t="s">
+        <v>189</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E44" s="35">
+        <v>146</v>
+      </c>
+      <c r="E44" s="34">
         <v>9.6</v>
       </c>
-      <c r="F44" s="35">
+      <c r="F44" s="34">
         <v>8.85</v>
       </c>
-      <c r="G44" s="35">
+      <c r="G44" s="34">
         <v>31.5</v>
       </c>
-      <c r="H44" s="35">
+      <c r="H44" s="34">
         <v>27.5</v>
       </c>
-      <c r="I44" s="35">
+      <c r="I44" s="34">
         <v>45</v>
       </c>
-      <c r="J44" s="36">
+      <c r="J44" s="35">
         <v>0.04</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="62" t="s">
-        <v>60</v>
+      <c r="A45" s="61" t="s">
+        <v>68</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E45" s="35">
+        <v>147</v>
+      </c>
+      <c r="E45" s="34">
         <v>0</v>
       </c>
-      <c r="F45" s="35">
+      <c r="F45" s="34">
         <v>0</v>
       </c>
-      <c r="G45" s="35">
+      <c r="G45" s="34">
         <v>0</v>
       </c>
-      <c r="H45" s="35">
+      <c r="H45" s="34">
         <v>0</v>
       </c>
-      <c r="I45" s="35">
+      <c r="I45" s="34">
         <v>0</v>
       </c>
-      <c r="J45" s="46">
+      <c r="J45" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="62" t="s">
-        <v>60</v>
+      <c r="A46" s="61" t="s">
+        <v>68</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E46" s="35">
+        <v>148</v>
+      </c>
+      <c r="E46" s="34">
         <v>10.5</v>
       </c>
-      <c r="F46" s="35">
+      <c r="F46" s="34">
         <v>9.5</v>
       </c>
-      <c r="G46" s="35">
+      <c r="G46" s="34">
         <v>39.5</v>
       </c>
-      <c r="H46" s="35">
+      <c r="H46" s="34">
         <v>27</v>
       </c>
-      <c r="I46" s="35">
+      <c r="I46" s="34">
         <v>42.5</v>
       </c>
-      <c r="J46" s="46">
+      <c r="J46" s="45">
         <v>0.05</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="16" t="s">
-        <v>63</v>
+    <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="77" t="s">
+        <v>68</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E47" s="35">
+      <c r="E47" s="34">
         <v>12.31</v>
       </c>
-      <c r="F47" s="35">
+      <c r="F47" s="34">
         <v>12</v>
       </c>
-      <c r="G47" s="35">
+      <c r="G47" s="34">
         <v>36</v>
       </c>
-      <c r="H47" s="35">
+      <c r="H47" s="34">
         <v>35.5</v>
       </c>
-      <c r="I47" s="35">
+      <c r="I47" s="34">
         <v>27.5</v>
       </c>
-      <c r="J47" s="46">
+      <c r="J47" s="45">
         <f t="shared" ref="J47" si="1">G47*H47*I47/1000000</f>
         <v>3.5145000000000003E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="16" t="s">
-        <v>65</v>
+    <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="69" t="s">
-        <v>185</v>
+        <v>61</v>
+      </c>
+      <c r="C48" s="64" t="s">
+        <v>178</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="35">
+        <v>62</v>
+      </c>
+      <c r="E48" s="34">
         <v>9.57</v>
       </c>
-      <c r="F48" s="35">
+      <c r="F48" s="34">
         <v>8.57</v>
       </c>
-      <c r="G48" s="35">
+      <c r="G48" s="34">
         <v>48.5</v>
       </c>
-      <c r="H48" s="35">
+      <c r="H48" s="34">
         <v>32.5</v>
       </c>
-      <c r="I48" s="35">
+      <c r="I48" s="34">
         <v>29</v>
       </c>
-      <c r="J48" s="36">
+      <c r="J48" s="35">
         <f>(G48*H48*I48)/1000000</f>
         <v>4.5711250000000002E-2</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="16" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="69" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="C49" s="64" t="s">
+        <v>58</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" s="35">
+        <v>64</v>
+      </c>
+      <c r="E49" s="34">
         <v>12</v>
       </c>
-      <c r="F49" s="35">
+      <c r="F49" s="34">
         <v>10</v>
       </c>
-      <c r="G49" s="35">
+      <c r="G49" s="34">
         <v>32.4</v>
       </c>
-      <c r="H49" s="35">
+      <c r="H49" s="34">
         <v>15</v>
       </c>
-      <c r="I49" s="35">
+      <c r="I49" s="34">
         <v>32</v>
       </c>
-      <c r="J49" s="36">
+      <c r="J49" s="35">
         <v>1.6E-2</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="46">
+        <v>15</v>
+      </c>
+      <c r="F50" s="46">
+        <v>14.15</v>
+      </c>
+      <c r="G50" s="46">
+        <v>41</v>
+      </c>
+      <c r="H50" s="46">
+        <v>30</v>
+      </c>
+      <c r="I50" s="46">
+        <v>45.5</v>
+      </c>
+      <c r="J50" s="47">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51" s="46">
+        <v>12.6</v>
+      </c>
+      <c r="F51" s="46">
+        <v>11.1</v>
+      </c>
+      <c r="G51" s="46">
+        <v>39.5</v>
+      </c>
+      <c r="H51" s="46">
+        <v>38.5</v>
+      </c>
+      <c r="I51" s="46">
+        <v>54.5</v>
+      </c>
+      <c r="J51" s="47">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="E52" s="46">
+        <v>25.3</v>
+      </c>
+      <c r="F52" s="46">
+        <v>22.4</v>
+      </c>
+      <c r="G52" s="46">
+        <v>57</v>
+      </c>
+      <c r="H52" s="46">
+        <v>53</v>
+      </c>
+      <c r="I52" s="46">
+        <v>55</v>
+      </c>
+      <c r="J52" s="47">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="76" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="63" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" s="57" t="s">
+        <v>151</v>
+      </c>
+      <c r="E53" s="46">
+        <v>8</v>
+      </c>
+      <c r="F53" s="46">
+        <v>7.5</v>
+      </c>
+      <c r="G53" s="46">
+        <v>45</v>
+      </c>
+      <c r="H53" s="46">
+        <v>37</v>
+      </c>
+      <c r="I53" s="46">
+        <v>28</v>
+      </c>
+      <c r="J53" s="47">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="B50" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C50" s="8" t="s">
+      <c r="C54" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="48">
+        <v>24</v>
+      </c>
+      <c r="F54" s="48">
+        <v>23</v>
+      </c>
+      <c r="G54" s="36">
+        <v>51.5</v>
+      </c>
+      <c r="H54" s="36">
+        <v>33.5</v>
+      </c>
+      <c r="I54" s="36">
+        <v>60</v>
+      </c>
+      <c r="J54" s="49">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="68"/>
+      <c r="C55" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" s="39">
+        <v>24.2</v>
+      </c>
+      <c r="F55" s="39">
+        <v>22.5</v>
+      </c>
+      <c r="G55" s="39">
+        <v>54</v>
+      </c>
+      <c r="H55" s="39">
+        <v>44</v>
+      </c>
+      <c r="I55" s="39">
+        <v>34</v>
+      </c>
+      <c r="J55" s="40">
+        <v>8.0783999999999995E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="B56" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="E50" s="47">
-        <v>15</v>
-      </c>
-      <c r="F50" s="47">
-        <v>14.15</v>
-      </c>
-      <c r="G50" s="47">
+      <c r="C56" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56" s="36">
+        <v>20</v>
+      </c>
+      <c r="F56" s="36">
+        <v>19</v>
+      </c>
+      <c r="G56" s="36">
+        <v>42.5</v>
+      </c>
+      <c r="H56" s="36">
+        <v>32</v>
+      </c>
+      <c r="I56" s="36">
+        <v>49</v>
+      </c>
+      <c r="J56" s="49">
+        <v>6.6640000000000005E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" s="74" t="s">
+        <v>187</v>
+      </c>
+      <c r="B57" s="67"/>
+      <c r="C57" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" s="37">
+        <v>26.8</v>
+      </c>
+      <c r="F57" s="37">
+        <v>25.8</v>
+      </c>
+      <c r="G57" s="37">
+        <v>46.5</v>
+      </c>
+      <c r="H57" s="37">
+        <v>36.5</v>
+      </c>
+      <c r="I57" s="37">
+        <v>55</v>
+      </c>
+      <c r="J57" s="38">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="H50" s="47">
-        <v>30</v>
-      </c>
-      <c r="I50" s="47">
-        <v>45.5</v>
-      </c>
-      <c r="J50" s="48">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="B51" s="9" t="s">
+      <c r="B58" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C51" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E51" s="47">
-        <v>12.6</v>
-      </c>
-      <c r="F51" s="47">
-        <v>11.1</v>
-      </c>
-      <c r="G51" s="47">
-        <v>39.5</v>
-      </c>
-      <c r="H51" s="47">
-        <v>38.5</v>
-      </c>
-      <c r="I51" s="47">
-        <v>54.5</v>
-      </c>
-      <c r="J51" s="48">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="63"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="68" t="s">
-        <v>85</v>
-      </c>
-      <c r="D52" s="58" t="s">
-        <v>157</v>
-      </c>
-      <c r="E52" s="47">
+      <c r="C58" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
+      <c r="H58" s="50"/>
+      <c r="I58" s="50"/>
+      <c r="J58" s="51"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="50">
+        <v>29.4</v>
+      </c>
+      <c r="F59" s="50">
+        <v>28</v>
+      </c>
+      <c r="G59" s="50">
+        <v>45</v>
+      </c>
+      <c r="H59" s="50">
+        <v>41</v>
+      </c>
+      <c r="I59" s="50">
+        <v>54</v>
+      </c>
+      <c r="J59" s="51">
+        <v>9.9629999999999996E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D60" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60" s="39">
+        <v>27</v>
+      </c>
+      <c r="F60" s="39">
         <v>25.3</v>
       </c>
-      <c r="F52" s="47">
-        <v>22.4</v>
-      </c>
-      <c r="G52" s="47">
-        <v>57</v>
-      </c>
-      <c r="H52" s="47">
-        <v>53</v>
-      </c>
-      <c r="I52" s="47">
-        <v>55</v>
-      </c>
-      <c r="J52" s="48">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="64"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="68" t="s">
-        <v>171</v>
-      </c>
-      <c r="D53" s="58" t="s">
-        <v>158</v>
-      </c>
-      <c r="E53" s="47">
-        <v>8</v>
-      </c>
-      <c r="F53" s="47">
-        <v>7.5</v>
-      </c>
-      <c r="G53" s="47">
-        <v>45</v>
-      </c>
-      <c r="H53" s="47">
-        <v>37</v>
-      </c>
-      <c r="I53" s="47">
+      <c r="G60" s="39">
+        <v>61.5</v>
+      </c>
+      <c r="H60" s="39">
+        <v>46</v>
+      </c>
+      <c r="I60" s="39">
+        <v>35</v>
+      </c>
+      <c r="J60" s="40">
+        <v>9.9015000000000006E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E61" s="34">
+        <v>7</v>
+      </c>
+      <c r="F61" s="34">
+        <v>6</v>
+      </c>
+      <c r="G61" s="34">
+        <v>29</v>
+      </c>
+      <c r="H61" s="34">
+        <v>24.5</v>
+      </c>
+      <c r="I61" s="34">
+        <v>16</v>
+      </c>
+      <c r="J61" s="35">
+        <v>1.1368E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" s="34">
+        <v>5.2</v>
+      </c>
+      <c r="F62" s="34">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G62" s="34">
         <v>28</v>
       </c>
-      <c r="J53" s="48">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="66" t="s">
-        <v>76</v>
-      </c>
-      <c r="B54" s="71" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="E54" s="49">
-        <v>24</v>
-      </c>
-      <c r="F54" s="49">
-        <v>23</v>
-      </c>
-      <c r="G54" s="37">
-        <v>51.5</v>
-      </c>
-      <c r="H54" s="37">
-        <v>33.5</v>
-      </c>
-      <c r="I54" s="37">
-        <v>60</v>
-      </c>
-      <c r="J54" s="50">
-        <v>0.104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="67"/>
-      <c r="B55" s="73"/>
-      <c r="C55" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="E55" s="40">
-        <v>24.2</v>
-      </c>
-      <c r="F55" s="40">
-        <v>22.5</v>
-      </c>
-      <c r="G55" s="40">
-        <v>54</v>
-      </c>
-      <c r="H55" s="40">
-        <v>44</v>
-      </c>
-      <c r="I55" s="40">
-        <v>34</v>
-      </c>
-      <c r="J55" s="41">
-        <v>8.0783999999999995E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A56" s="60" t="s">
-        <v>78</v>
-      </c>
-      <c r="B56" s="71" t="s">
-        <v>79</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D56" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E56" s="37">
-        <v>20</v>
-      </c>
-      <c r="F56" s="37">
-        <v>19</v>
-      </c>
-      <c r="G56" s="37">
-        <v>42.5</v>
-      </c>
-      <c r="H56" s="37">
-        <v>32</v>
-      </c>
-      <c r="I56" s="37">
-        <v>49</v>
-      </c>
-      <c r="J56" s="50">
-        <v>6.6640000000000005E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A57" s="59"/>
-      <c r="B57" s="72"/>
-      <c r="C57" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="E57" s="38">
-        <v>26.8</v>
-      </c>
-      <c r="F57" s="38">
-        <v>25.8</v>
-      </c>
-      <c r="G57" s="38">
-        <v>46.5</v>
-      </c>
-      <c r="H57" s="38">
-        <v>36.5</v>
-      </c>
-      <c r="I57" s="38">
-        <v>55</v>
-      </c>
-      <c r="J57" s="39">
-        <v>9.4E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A58" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D58" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58" s="51"/>
-      <c r="F58" s="51"/>
-      <c r="G58" s="51"/>
-      <c r="H58" s="51"/>
-      <c r="I58" s="51"/>
-      <c r="J58" s="52"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A59" s="65" t="s">
-        <v>82</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D59" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59" s="51">
-        <v>29.4</v>
-      </c>
-      <c r="F59" s="51">
-        <v>28</v>
-      </c>
-      <c r="G59" s="51">
-        <v>45</v>
-      </c>
-      <c r="H59" s="51">
+      <c r="H62" s="34">
+        <v>25</v>
+      </c>
+      <c r="I62" s="34">
+        <v>48</v>
+      </c>
+      <c r="J62" s="35">
+        <v>3.3000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="I59" s="51">
-        <v>54</v>
-      </c>
-      <c r="J59" s="52">
-        <v>9.9629999999999996E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="61"/>
-      <c r="B60" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D60" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="E60" s="40">
-        <v>27</v>
-      </c>
-      <c r="F60" s="40">
-        <v>25.3</v>
-      </c>
-      <c r="G60" s="40">
-        <v>61.5</v>
-      </c>
-      <c r="H60" s="40">
-        <v>46</v>
-      </c>
-      <c r="I60" s="40">
-        <v>35</v>
-      </c>
-      <c r="J60" s="41">
-        <v>9.9015000000000006E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="15" t="s">
+      <c r="B63" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E61" s="35">
-        <v>7</v>
-      </c>
-      <c r="F61" s="35">
+      <c r="E63" s="34">
+        <v>4.8</v>
+      </c>
+      <c r="F63" s="34">
         <v>6</v>
       </c>
-      <c r="G61" s="35">
-        <v>29</v>
-      </c>
-      <c r="H61" s="35">
-        <v>24.5</v>
-      </c>
-      <c r="I61" s="35">
-        <v>16</v>
-      </c>
-      <c r="J61" s="36">
-        <v>1.1368E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B62" s="1" t="s">
+      <c r="G63" s="34">
+        <v>37.6</v>
+      </c>
+      <c r="H63" s="34">
+        <v>37.6</v>
+      </c>
+      <c r="I63" s="34">
+        <v>25.2</v>
+      </c>
+      <c r="J63" s="35">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D62" s="3" t="s">
+      <c r="C64" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E62" s="35">
-        <v>5.2</v>
-      </c>
-      <c r="F62" s="35">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="G62" s="35">
-        <v>28</v>
-      </c>
-      <c r="H62" s="35">
-        <v>25</v>
-      </c>
-      <c r="I62" s="35">
-        <v>48</v>
-      </c>
-      <c r="J62" s="36">
-        <v>3.3000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E63" s="35">
-        <v>4.8</v>
-      </c>
-      <c r="F63" s="35">
-        <v>6</v>
-      </c>
-      <c r="G63" s="35">
-        <v>37.6</v>
-      </c>
-      <c r="H63" s="35">
-        <v>37.6</v>
-      </c>
-      <c r="I63" s="35">
-        <v>25.2</v>
-      </c>
-      <c r="J63" s="36">
-        <v>3.5999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="D64" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E64" s="35">
+        <v>90</v>
+      </c>
+      <c r="E64" s="34">
         <v>11</v>
       </c>
-      <c r="F64" s="35">
+      <c r="F64" s="34">
         <v>10</v>
       </c>
-      <c r="G64" s="35">
+      <c r="G64" s="34">
         <v>41.5</v>
       </c>
-      <c r="H64" s="35">
+      <c r="H64" s="34">
         <v>27.5</v>
       </c>
-      <c r="I64" s="35">
+      <c r="I64" s="34">
         <v>21</v>
       </c>
-      <c r="J64" s="36">
+      <c r="J64" s="35">
         <v>2.3966250000000001E-2</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="15" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65" s="35">
+        <v>17</v>
+      </c>
+      <c r="E65" s="34">
         <v>15</v>
       </c>
-      <c r="F65" s="35">
+      <c r="F65" s="34">
         <v>14</v>
       </c>
-      <c r="G65" s="35">
+      <c r="G65" s="34">
         <v>63</v>
       </c>
-      <c r="H65" s="35">
+      <c r="H65" s="34">
         <v>32</v>
       </c>
-      <c r="I65" s="35">
+      <c r="I65" s="34">
         <v>41</v>
       </c>
-      <c r="J65" s="36">
+      <c r="J65" s="35">
         <f>G65*H65*I65/1000000</f>
         <v>8.2655999999999993E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="16" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E66" s="35">
+        <v>95</v>
+      </c>
+      <c r="E66" s="34">
         <v>10.5</v>
       </c>
-      <c r="F66" s="35">
+      <c r="F66" s="34">
         <v>9.6999999999999993</v>
       </c>
       <c r="G66" s="3">
@@ -4757,324 +4772,353 @@
       <c r="I66" s="3">
         <v>46</v>
       </c>
-      <c r="J66" s="53">
+      <c r="J66" s="52">
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="15" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E67" s="35">
+        <v>98</v>
+      </c>
+      <c r="E67" s="34">
         <v>6.5</v>
       </c>
-      <c r="F67" s="35">
+      <c r="F67" s="34">
         <v>5</v>
       </c>
-      <c r="G67" s="35">
+      <c r="G67" s="34">
         <v>33.5</v>
       </c>
-      <c r="H67" s="35">
+      <c r="H67" s="34">
         <v>29</v>
       </c>
-      <c r="I67" s="35">
+      <c r="I67" s="34">
         <v>32</v>
       </c>
-      <c r="J67" s="36">
+      <c r="J67" s="35">
         <f t="shared" ref="J67" si="2">+G67*H67*I67/1000000</f>
         <v>3.1088000000000001E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="15" t="s">
-        <v>105</v>
+    <row r="68" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="72" t="s">
+        <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E68" s="35">
+        <v>58</v>
+      </c>
+      <c r="E68" s="34">
         <v>10.72</v>
       </c>
-      <c r="F68" s="35">
+      <c r="F68" s="34">
         <v>9.7200000000000006</v>
       </c>
-      <c r="G68" s="35">
+      <c r="G68" s="34">
         <v>28</v>
       </c>
-      <c r="H68" s="35">
+      <c r="H68" s="34">
         <v>28</v>
       </c>
-      <c r="I68" s="35">
+      <c r="I68" s="34">
         <v>34.5</v>
       </c>
-      <c r="J68" s="35">
+      <c r="J68" s="34">
         <v>2.7047999999999999E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="16" t="s">
-        <v>107</v>
+    <row r="69" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="15" t="s">
+        <v>11</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C69" s="70" t="s">
-        <v>62</v>
+        <v>102</v>
+      </c>
+      <c r="C69" s="65" t="s">
+        <v>58</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E69" s="35">
+        <v>58</v>
+      </c>
+      <c r="E69" s="34">
         <v>11.4</v>
       </c>
-      <c r="F69" s="35">
+      <c r="F69" s="34">
         <v>11</v>
       </c>
-      <c r="G69" s="35">
+      <c r="G69" s="34">
         <v>37.5</v>
       </c>
-      <c r="H69" s="35">
+      <c r="H69" s="34">
         <v>28.2</v>
       </c>
-      <c r="I69" s="35">
+      <c r="I69" s="34">
         <v>34.799999999999997</v>
       </c>
-      <c r="J69" s="36">
+      <c r="J69" s="35">
         <f t="shared" ref="J69" si="3">+G69*H69*I69/1000000</f>
         <v>3.6801E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="16" t="s">
+    <row r="70" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E70" s="34">
+        <v>12.75</v>
+      </c>
+      <c r="F70" s="34">
+        <v>11.2</v>
+      </c>
+      <c r="G70" s="34">
+        <v>37.5</v>
+      </c>
+      <c r="H70" s="34">
+        <v>28.2</v>
+      </c>
+      <c r="I70" s="34">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="J70" s="35">
+        <v>3.6801E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E71" s="34">
+        <v>13</v>
+      </c>
+      <c r="F71" s="34">
+        <v>11</v>
+      </c>
+      <c r="G71" s="34">
+        <v>35</v>
+      </c>
+      <c r="H71" s="34">
+        <v>22</v>
+      </c>
+      <c r="I71" s="34">
+        <v>39</v>
+      </c>
+      <c r="J71" s="34">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C70" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E72" s="34">
+        <v>10.46</v>
+      </c>
+      <c r="F72" s="34">
+        <v>8.4</v>
+      </c>
+      <c r="G72" s="53">
+        <v>28.4</v>
+      </c>
+      <c r="H72" s="53">
+        <v>31.6</v>
+      </c>
+      <c r="I72" s="54">
+        <v>30</v>
+      </c>
+      <c r="J72" s="35">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E70" s="35">
-        <v>12.75</v>
-      </c>
-      <c r="F70" s="35">
-        <v>11.2</v>
-      </c>
-      <c r="G70" s="35">
-        <v>37.5</v>
-      </c>
-      <c r="H70" s="35">
-        <v>28.2</v>
-      </c>
-      <c r="I70" s="35">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="J70" s="36">
-        <v>3.6801E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="16" t="s">
+      <c r="C73" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E71" s="35">
-        <v>13</v>
-      </c>
-      <c r="F71" s="35">
-        <v>11</v>
-      </c>
-      <c r="G71" s="35">
-        <v>35</v>
-      </c>
-      <c r="H71" s="35">
-        <v>22</v>
-      </c>
-      <c r="I71" s="35">
-        <v>39</v>
-      </c>
-      <c r="J71" s="35">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E72" s="35">
-        <v>10.46</v>
-      </c>
-      <c r="F72" s="35">
-        <v>8.4</v>
-      </c>
-      <c r="G72" s="54">
-        <v>28.4</v>
-      </c>
-      <c r="H72" s="54">
-        <v>31.6</v>
-      </c>
-      <c r="I72" s="55">
-        <v>30</v>
-      </c>
-      <c r="J72" s="36">
-        <v>2.7E-2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="D73" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E73" s="35">
+        <v>112</v>
+      </c>
+      <c r="E73" s="34">
         <v>11.5</v>
       </c>
-      <c r="F73" s="35">
+      <c r="F73" s="34">
         <v>10.5</v>
       </c>
-      <c r="G73" s="35">
+      <c r="G73" s="34">
         <v>63</v>
       </c>
-      <c r="H73" s="35">
+      <c r="H73" s="34">
         <v>54.5</v>
       </c>
-      <c r="I73" s="35">
+      <c r="I73" s="34">
         <v>28.5</v>
       </c>
-      <c r="J73" s="35">
+      <c r="J73" s="34">
         <f t="shared" ref="J73:J74" si="4">G73*H73*I73/1000000</f>
         <v>9.7854750000000004E-2</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="15" t="s">
-        <v>119</v>
+      <c r="A74" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E74" s="35">
+        <v>115</v>
+      </c>
+      <c r="E74" s="34">
         <v>14</v>
       </c>
-      <c r="F74" s="35">
+      <c r="F74" s="34">
         <v>13.1</v>
       </c>
-      <c r="G74" s="35">
+      <c r="G74" s="34">
         <v>52.5</v>
       </c>
-      <c r="H74" s="35">
+      <c r="H74" s="34">
         <v>52.5</v>
       </c>
-      <c r="I74" s="35">
+      <c r="I74" s="34">
         <v>29</v>
       </c>
-      <c r="J74" s="35">
+      <c r="J74" s="34">
         <f t="shared" si="4"/>
         <v>7.9931249999999995E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="16" t="s">
-        <v>122</v>
-      </c>
+    <row r="75" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="72"/>
       <c r="B75" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E75" s="35">
+        <v>118</v>
+      </c>
+      <c r="E75" s="34">
         <v>9.65</v>
       </c>
-      <c r="F75" s="35">
+      <c r="F75" s="34">
         <v>9</v>
       </c>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
-      <c r="J75" s="36">
+      <c r="G75" s="34"/>
+      <c r="H75" s="34"/>
+      <c r="I75" s="34"/>
+      <c r="J75" s="35">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="16" t="s">
-        <v>125</v>
-      </c>
+    <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="70"/>
       <c r="B76" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C76" s="70">
+        <v>117</v>
+      </c>
+      <c r="C76" s="65">
         <v>4</v>
       </c>
       <c r="D76" s="3">
         <v>4</v>
       </c>
-      <c r="E76" s="35">
+      <c r="E76" s="34">
         <v>12.8</v>
       </c>
-      <c r="F76" s="35">
+      <c r="F76" s="34">
         <v>12</v>
       </c>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
-      <c r="J76" s="36">
+      <c r="G76" s="34"/>
+      <c r="H76" s="34"/>
+      <c r="I76" s="34"/>
+      <c r="J76" s="35">
         <v>6.2E-2</v>
       </c>
     </row>
+    <row r="77" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="59"/>
+      <c r="B77" s="59" t="s">
+        <v>184</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E77" s="3">
+        <v>19.78</v>
+      </c>
+      <c r="F77" s="3">
+        <v>18.170000000000002</v>
+      </c>
+      <c r="G77" s="3">
+        <v>61</v>
+      </c>
+      <c r="H77" s="3">
+        <v>57</v>
+      </c>
+      <c r="I77" s="3">
+        <v>28.5</v>
+      </c>
+      <c r="J77" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J76" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A77">
+    <sortCondition ref="A8:A77"/>
+  </sortState>
   <mergeCells count="2">
     <mergeCell ref="B56:B57"/>
     <mergeCell ref="B54:B55"/>
